--- a/3-能力管理/运行记录类文件/030204-2025年4-12月运维服务能力改进计划及跟踪.xlsx
+++ b/3-能力管理/运行记录类文件/030204-2025年4-12月运维服务能力改进计划及跟踪.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9575"/>
+    <workbookView windowHeight="18180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -135,42 +135,7 @@
     <t>满意度调查评分较低</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>由服</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>务台负责人进行集体培训来提高服务台人员的用语规</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>范性，从而提高用户的整体满</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>意度。</t>
-    </r>
+    <t>由服务台负责人进行集体培训来提高服务台人员的用语规范性，从而提高用户的整体满意度。</t>
   </si>
 </sst>
 </file>
@@ -183,7 +148,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -207,11 +172,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -353,12 +317,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -742,7 +700,7 @@
     </border>
   </borders>
   <cellStyleXfs count="55">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
@@ -800,7 +758,7 @@
     <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -828,6 +786,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="55">
@@ -1184,15 +1145,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="2" max="2" width="12.25" customWidth="1"/>
-    <col min="4" max="4" width="17.8796296296296" customWidth="1"/>
-    <col min="5" max="5" width="26.6296296296296" customWidth="1"/>
+    <col min="4" max="4" width="17.8833333333333" customWidth="1"/>
+    <col min="5" max="5" width="26.6333333333333" customWidth="1"/>
     <col min="6" max="6" width="12.75" customWidth="1"/>
-    <col min="7" max="7" width="13.7777777777778" customWidth="1"/>
+    <col min="7" max="7" width="13.775" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="12.3796296296296" customWidth="1"/>
+    <col min="9" max="9" width="12.3833333333333" customWidth="1"/>
     <col min="10" max="10" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1290,7 +1251,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="48" spans="1:10">
+    <row r="5" ht="36" spans="1:10">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -1322,7 +1283,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" ht="62.4" spans="1:10">
+    <row r="6" ht="57" spans="1:10">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -1335,7 +1296,7 @@
       <c r="D6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="10" t="s">
         <v>34</v>
       </c>
       <c r="F6" s="3" t="s">

--- a/3-能力管理/运行记录类文件/030204-2025年4-12月运维服务能力改进计划及跟踪.xlsx
+++ b/3-能力管理/运行记录类文件/030204-2025年4-12月运维服务能力改进计划及跟踪.xlsx
@@ -75,7 +75,7 @@
     <t>服务流程管理</t>
   </si>
   <si>
-    <t>运维部曾在 2025年10月 15 日组织过服务知识评审会，但内审员在检查其评审会对应的记录单时，未能提供《服务知识评审记录》</t>
+    <t>运维部曾在 2025年12月 15 日组织过服务知识评审会，但内审员在检查其评审会对应的记录单时，未能提供《服务知识评审记录》</t>
   </si>
   <si>
     <t>1.部门内部增加内部审核环节，每个月最后一天检查服务报告。

--- a/3-能力管理/运行记录类文件/030204-2025年4-12月运维服务能力改进计划及跟踪.xlsx
+++ b/3-能力管理/运行记录类文件/030204-2025年4-12月运维服务能力改进计划及跟踪.xlsx
@@ -30,7 +30,7 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t xml:space="preserve">
-2025年运维服务能力改进计划及跟踪</t>
+运维服务能力改进计划及跟踪</t>
   </si>
   <si>
     <t>序号</t>
@@ -95,7 +95,7 @@
     <t>2025.12.16</t>
   </si>
   <si>
-    <t>李平</t>
+    <t>秦立祥</t>
   </si>
   <si>
     <t>最终软件库考核指标</t>
